--- a/filer/28504799_iss.xlsx
+++ b/filer/28504799_iss.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3954,6 +3955,148 @@
       </c>
       <c r="F81" s="13">
         <f>IFERROR($F$28/($F$47+$F$50)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B84" s="17">
+        <f>'pengestrom_raw'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C84" s="17">
+        <f>'pengestrom_raw'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D84" s="17">
+        <f>'pengestrom_raw'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E84" s="17">
+        <f>'pengestrom_raw'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F84" s="17">
+        <f>'pengestrom_raw'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B85" s="17">
+        <f>'pengestrom_raw'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C85" s="17">
+        <f>'pengestrom_raw'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>'pengestrom_raw'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>'pengestrom_raw'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>'pengestrom_raw'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B86" s="17">
+        <f>'pengestrom_raw'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C86" s="17">
+        <f>'pengestrom_raw'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D86" s="17">
+        <f>'pengestrom_raw'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E86" s="17">
+        <f>'pengestrom_raw'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F86" s="17">
+        <f>'pengestrom_raw'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B87" s="17">
+        <f>'pengestrom_raw'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C87" s="17">
+        <f>'pengestrom_raw'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D87" s="17">
+        <f>'pengestrom_raw'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E87" s="17">
+        <f>'pengestrom_raw'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F87" s="17">
+        <f>'pengestrom_raw'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B88">
+        <f>IF(ABS(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C88">
+        <f>IF(ABS(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D88">
+        <f>IF(ABS(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E88">
+        <f>IF(ABS(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F88">
+        <f>IF(ABS(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4002,317 +4145,317 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>71363000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>76538000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>78681000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>83761000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>84684000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>46369000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>48329000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>49607000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>52822000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>53888000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>1760000</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>1517000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>1464000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>1469000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>1555000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>1701000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>2835000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>3138000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>3889000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>3950000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>41000</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>207000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>185000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>314000</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>258000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>697000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>596000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>792000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>904000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>919000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>1045000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>2446000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>2531000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>3299000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>3289000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>509000</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>441000</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>554000</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>658000</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>676000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>536000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>2005000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>1977000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>2641000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>2613000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4359,710 +4502,710 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>22739000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>23920000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>23272000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>24359000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>24208000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>2445000</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>2403000</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>2200000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>2424000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>2229000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>457000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>512000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>195000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>605000</v>
       </c>
-      <c r="F5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>27362000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>28664000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>27555000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>29271000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>29017000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>5020000</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>6598000</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>7323000</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>7519000</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>7170000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>177000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>231000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>239000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>251000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>245000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>10406000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>10996000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>11354000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>12449000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>12872000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>790000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>912000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>962000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>885000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>822000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>185000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>173000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>126000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>120000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>115000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>1582000</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>1695000</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>1628000</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>1721000</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>1623000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>3428000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>5214000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>6093000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>6829000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>1729000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>16293000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>18341000</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>20138000</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>21370000</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>16584000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>43655000</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>47005000</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>47693000</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>50641000</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>45601000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>7583000</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>10156000</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>9893000</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>11143000</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <v>9776000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>976000</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>1178000</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>1320000</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>1156000</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="17" t="n">
         <v>1143000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>1351000</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>1185000</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>1135000</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>1316000</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>1104000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>16094000</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>15945000</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>13427000</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>13584000</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>9762000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>888000</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>963000</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>3292000</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>4757000</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <v>5315000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>5657000</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>6952000</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>7259000</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>7387000</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>6955000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>8730000</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>8714000</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>8482000</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>9505000</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>9735000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>16690000</v>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>17417000</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>20902000</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>22300000</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="17" t="n">
         <v>22741000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>35866000</v>
       </c>
-      <c r="C40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>36190000</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>37171000</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>38728000</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="F40" s="17" t="n">
         <v>35061000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>43655000</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>47005000</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>47693000</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="17" t="n">
         <v>50641000</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="F41" s="17" t="n">
         <v>45601000</v>
       </c>
     </row>
@@ -5072,6 +5215,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>3221000</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>3333000</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>3392000</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>3727000</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>3989000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>73000</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-546000</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-1042000</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-1536000</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-1184000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-2832000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-930000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-1334000</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-1405000</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-7638000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6294,7 +6559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
